--- a/assets/kinyu-doboku.xlsx
+++ b/assets/kinyu-doboku.xlsx
@@ -656,7 +656,7 @@
     <row r="16" ht="52" customHeight="1">
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　https://morikosha.com/ で、淡・玄・雅・粋・理の5案をご覧いただけます。どれを選んでも、載る項目は同じです。「希望デザイン」の欄に案名をお書きください。</t>
+          <t xml:space="preserve">　https://morikosha.com/ で、淡（あわい）・玄（げん）・雅（みやび）・粋（いき）・理（り）の5案をご覧いただけます。どれを選んでも、載る項目は同じです。「希望デザイン」の欄にお書きください。</t>
         </is>
       </c>
     </row>
@@ -897,7 +897,7 @@
       </c>
       <c r="E7" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">morikosha.com で5案（淡・玄・雅・粋・理）の実物をご覧いただけます。「理」または「5案「理」」のようにお書きください。載る項目は、どの案も同じです。</t>
+          <t>morikosha.com で5案（淡・玄・雅・粋・理）の実物をご覧いただけます。「1案「淡」」のようにお書きください。載る項目は、どの案も同じです。</t>
         </is>
       </c>
     </row>

--- a/assets/kinyu-doboku.xlsx
+++ b/assets/kinyu-doboku.xlsx
@@ -798,7 +798,7 @@
     <row r="47" ht="20" customHeight="1">
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>ご記入いただく欄は全部で 38 です（うち【必須】は 10 ）。</t>
+          <t>ご記入いただく欄は全部で 39 です（うち【必須】は 10 ）。</t>
         </is>
       </c>
     </row>
@@ -813,7 +813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:E60"/>
+  <dimension ref="A2:E61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -1799,6 +1799,24 @@
         </is>
       </c>
     </row>
+    <row r="61" ht="78" customHeight="1">
+      <c r="B61" s="19" t="inlineStr">
+        <is>
+          <t>杜工舎の制作例として紹介してよいか</t>
+        </is>
+      </c>
+      <c r="C61" s="16" t="inlineStr"/>
+      <c r="D61" s="17" t="inlineStr">
+        <is>
+          <t>選ぶだけ（任意）</t>
+        </is>
+      </c>
+      <c r="E61" s="18" t="inlineStr">
+        <is>
+          <t>「紹介してよい」とお書きいただいた場合だけ、杜工舎のホームページの制作例として、御社の社名とページへのリンクを載せます。空欄なら載せません。お礼や値引きはなく、お断りいただいても制作の内容は変わりません。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/assets/kinyu-doboku.xlsx
+++ b/assets/kinyu-doboku.xlsx
@@ -798,7 +798,7 @@
     <row r="47" ht="20" customHeight="1">
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>ご記入いただく欄は全部で 39 です（うち【必須】は 10 ）。</t>
+          <t>ご記入いただく欄は全部で 38 です（うち【必須】は 10 ）。</t>
         </is>
       </c>
     </row>
@@ -813,7 +813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:E61"/>
+  <dimension ref="A2:E60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -1799,24 +1799,6 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="78" customHeight="1">
-      <c r="B61" s="19" t="inlineStr">
-        <is>
-          <t>杜工舎の制作例として紹介してよいか</t>
-        </is>
-      </c>
-      <c r="C61" s="16" t="inlineStr"/>
-      <c r="D61" s="17" t="inlineStr">
-        <is>
-          <t>選ぶだけ（任意）</t>
-        </is>
-      </c>
-      <c r="E61" s="18" t="inlineStr">
-        <is>
-          <t>「紹介してよい」とお書きいただいた場合だけ、杜工舎のホームページの制作例として、御社の社名とページへのリンクを載せます。空欄なら載せません。お礼や値引きはなく、お断りいただいても制作の内容は変わりません。</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
